--- a/pipelines/Demo_data/Output_data/out_ИТ.Прочее.xlsx
+++ b/pipelines/Demo_data/Output_data/out_ИТ.Прочее.xlsx
@@ -486,10 +486,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -530,10 +528,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -574,10 +570,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F4" t="n">
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -618,10 +612,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -662,10 +654,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -706,10 +696,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -750,10 +738,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -794,10 +780,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -838,10 +822,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F10" t="n">
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -882,10 +864,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,10 +906,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F12" t="n">
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -970,10 +948,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1014,10 +990,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F14" t="n">
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1058,10 +1032,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1102,10 +1074,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1146,10 +1116,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1190,10 +1158,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F18" t="n">
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1234,10 +1200,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1278,10 +1242,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F20" t="n">
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1322,10 +1284,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F21" t="n">
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1366,10 +1326,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F22" t="n">
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1410,10 +1368,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F23" t="n">
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1454,10 +1410,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F24" t="n">
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1498,10 +1452,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F25" t="n">
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1542,10 +1494,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F26" t="n">
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1586,10 +1536,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F27" t="n">
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1630,10 +1578,8 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F28" t="n">
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>

--- a/pipelines/Demo_data/Output_data/out_ИТ.Прочее.xlsx
+++ b/pipelines/Demo_data/Output_data/out_ИТ.Прочее.xlsx
@@ -486,8 +486,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -528,8 +530,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -570,8 +574,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -612,8 +618,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -654,8 +662,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -696,8 +706,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -738,8 +750,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -780,8 +794,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -822,8 +838,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -864,8 +882,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -906,8 +926,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -948,8 +970,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -990,8 +1014,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1032,8 +1058,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1074,8 +1102,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1116,8 +1146,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1158,8 +1190,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1200,8 +1234,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1242,8 +1278,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1284,8 +1322,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1326,8 +1366,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1368,8 +1410,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1410,8 +1454,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1452,8 +1498,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1494,8 +1542,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1536,8 +1586,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1578,8 +1630,10 @@
           <t>604************</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
